--- a/wombat_Y2SiO5_example/reciprocal_space_conversion_Y2SiO5.xlsx
+++ b/wombat_Y2SiO5_example/reciprocal_space_conversion_Y2SiO5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\wombat_instrument_work\eulerian_cradle\Wombat_DMCpy\wombat_Y2SiO5_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\wombat_instrument_work\eulerian_cradle\Wombat_DMCpy\wombat_Y2SiO5_example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7958B233-5408-4853-B4B8-B2B0CCC28941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0DB067-2416-4887-B273-FF2928637730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-26760" yWindow="2160" windowWidth="21600" windowHeight="12510" activeTab="1" xr2:uid="{1785FB5C-C68B-4CD0-A3EB-01061EC28F90}"/>
   </bookViews>
@@ -589,25 +589,25 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>-6.0999999999999999E-2</v>
+        <v>-6.4000000000000001E-2</v>
       </c>
       <c r="B5">
-        <v>2.1349999999999998</v>
+        <v>2.145</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>-5.0000000000000001E-3</v>
       </c>
       <c r="D5">
         <f>SQRT(A5^2+B5^2+C5^2)</f>
-        <v>2.1358712508014146</v>
+        <v>2.1459603910603753</v>
       </c>
       <c r="E5">
         <f>2*PI()/D5</f>
-        <v>2.9417434711113932</v>
+        <v>2.9279129910104724</v>
       </c>
       <c r="F5">
         <f>DEGREES(2*ASIN($F$2/(2*E5)))</f>
-        <v>48.362061847141796</v>
+        <v>48.605228839417563</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -621,89 +621,89 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>-0.61299999999999999</v>
+        <v>-3.972</v>
       </c>
       <c r="B6">
-        <v>1.2769999999999999</v>
+        <v>-1.7649999999999999</v>
       </c>
       <c r="C6">
-        <v>3.5000000000000003E-2</v>
+        <v>-0.15490000000000001</v>
       </c>
       <c r="D6">
         <f>SQRT(A6^2+B6^2+C6^2)</f>
-        <v>1.4169414243362355</v>
+        <v>4.3492531554279523</v>
       </c>
       <c r="E6">
         <f>2*PI()/D6</f>
-        <v>4.4343296054901753</v>
+        <v>1.4446584465514611</v>
       </c>
       <c r="F6">
         <f>DEGREES(2*ASIN($F$2/(2*E6)))</f>
-        <v>31.536076631273499</v>
+        <v>113.0459740830986</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>-1.22</v>
+        <v>-4.0270000000000001</v>
       </c>
       <c r="B7">
-        <v>2.5579999999999998</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="C7">
-        <v>3.5000000000000003E-2</v>
+        <v>-0.16489999999999999</v>
       </c>
       <c r="D7">
         <f t="shared" ref="D7:D23" si="0">SQRT(A7^2+B7^2+C7^2)</f>
-        <v>2.8342528115889731</v>
+        <v>4.048626558476343</v>
       </c>
       <c r="E7">
         <f t="shared" ref="E7:E23" si="1">2*PI()/D7</f>
-        <v>2.2168753900457565</v>
+        <v>1.5519300721932219</v>
       </c>
       <c r="F7">
         <f t="shared" ref="F7:F23" si="2">DEGREES(2*ASIN($F$2/(2*E7)))</f>
-        <v>65.852333004621201</v>
+        <v>101.87381673624584</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>-1.6990000000000001</v>
+        <v>-1.7050000000000001</v>
       </c>
       <c r="B8">
-        <v>-0.45100000000000001</v>
+        <v>-0.45300000000000001</v>
       </c>
       <c r="C8">
-        <v>6.5000000000000002E-2</v>
+        <v>-8.4900000000000003E-2</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>1.759041500363195</v>
+        <v>1.7661942163873146</v>
       </c>
       <c r="E8">
         <f t="shared" si="1"/>
-        <v>3.5719369360428828</v>
+        <v>3.5574713408537884</v>
       </c>
       <c r="F8">
         <f t="shared" si="2"/>
-        <v>39.431248595931031</v>
+        <v>39.598273052151043</v>
       </c>
       <c r="H8">
         <v>4</v>
@@ -716,26 +716,17 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>-2.863</v>
-      </c>
-      <c r="B9">
-        <v>-3.4000000000000002E-2</v>
-      </c>
-      <c r="C9">
-        <v>0.1149</v>
-      </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>2.8655064142311741</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="1"/>
-        <v>2.1926962982790559</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="2"/>
-        <v>66.672527660291266</v>
+        <v>0</v>
+      </c>
+      <c r="E9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F9" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">

--- a/wombat_Y2SiO5_example/reciprocal_space_conversion_Y2SiO5.xlsx
+++ b/wombat_Y2SiO5_example/reciprocal_space_conversion_Y2SiO5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\wombat_instrument_work\eulerian_cradle\Wombat_DMCpy\wombat_Y2SiO5_example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0DB067-2416-4887-B273-FF2928637730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D506A0-2853-4D44-B1C8-0290344DB2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26760" yWindow="2160" windowWidth="21600" windowHeight="12510" activeTab="1" xr2:uid="{1785FB5C-C68B-4CD0-A3EB-01061EC28F90}"/>
+    <workbookView xWindow="-25650" yWindow="4545" windowWidth="21600" windowHeight="12510" activeTab="1" xr2:uid="{1785FB5C-C68B-4CD0-A3EB-01061EC28F90}"/>
   </bookViews>
   <sheets>
     <sheet name="2theta_to_Q" sheetId="2" r:id="rId1"/>
@@ -118,12 +118,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -138,8 +144,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,13 +595,13 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>-6.4000000000000001E-2</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>2.145</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>-5.0000000000000001E-3</v>
       </c>
       <c r="D5">
@@ -609,24 +616,24 @@
         <f>DEGREES(2*ASIN($F$2/(2*E5)))</f>
         <v>48.605228839417563</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>2</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>-3.972</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>-1.7649999999999999</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-0.15490000000000001</v>
       </c>
       <c r="D6">
@@ -641,13 +648,13 @@
         <f>DEGREES(2*ASIN($F$2/(2*E6)))</f>
         <v>113.0459740830986</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>4</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
         <v>-4</v>
       </c>
     </row>
@@ -716,17 +723,35 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>-4.47</v>
+      </c>
+      <c r="B9">
+        <v>-0.27189999999999998</v>
+      </c>
+      <c r="C9">
+        <v>0.317</v>
+      </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F9" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>4.4894675196508551</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>1.399539094486695</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="2"/>
+        <v>118.85758906897046</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>-4</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">

--- a/wombat_Y2SiO5_example/reciprocal_space_conversion_Y2SiO5.xlsx
+++ b/wombat_Y2SiO5_example/reciprocal_space_conversion_Y2SiO5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\wombat_instrument_work\eulerian_cradle\Wombat_DMCpy\wombat_Y2SiO5_example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D506A0-2853-4D44-B1C8-0290344DB2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D80226-766F-485C-8E66-B2EA08A6B402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25650" yWindow="4545" windowWidth="21600" windowHeight="12510" activeTab="1" xr2:uid="{1785FB5C-C68B-4CD0-A3EB-01061EC28F90}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{1785FB5C-C68B-4CD0-A3EB-01061EC28F90}"/>
   </bookViews>
   <sheets>
     <sheet name="2theta_to_Q" sheetId="2" r:id="rId1"/>
@@ -127,7 +127,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -144,8 +144,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -162,6 +163,34 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B41BE972-CB34-4A99-8C8E-F9CCF059B4A6}" name="Table1" displayName="Table1" ref="A4:J19" totalsRowShown="0">
+  <autoFilter ref="A4:J19" xr:uid="{B41BE972-CB34-4A99-8C8E-F9CCF059B4A6}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:J19">
+    <sortCondition ref="F4:F19"/>
+  </sortState>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{12FBD9A9-996A-4CE8-BF2C-9D8DB76DB7E0}" name="Qx (AA^-1)"/>
+    <tableColumn id="2" xr3:uid="{68A84B0B-23F3-4631-AE9F-03F7BD5417D6}" name="Qy (AA^-1)"/>
+    <tableColumn id="3" xr3:uid="{FB6D0B0A-C7F6-4D58-8C84-7A8E2B8604A1}" name="Qz (AA^-1)"/>
+    <tableColumn id="4" xr3:uid="{FF2D133C-86FE-4F7F-BF2B-CC15357C653E}" name="Q (AA^-1)">
+      <calculatedColumnFormula>SQRT(A5^2+B5^2+C5^2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{012FE562-A178-4A1F-89BA-92500E76E51F}" name="d (AA)">
+      <calculatedColumnFormula>2*PI()/D5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{17095612-0EFF-4DBC-8220-1183E693D2FF}" name="2θ (deg)">
+      <calculatedColumnFormula>DEGREES(2*ASIN($F$2/(2*E5)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{135A9FD9-E4C8-4BF4-8ED7-C4D61F920A92}" name="Notes"/>
+    <tableColumn id="8" xr3:uid="{76F3069A-9656-4971-B764-D690563FB720}" name="h"/>
+    <tableColumn id="9" xr3:uid="{DDC3777A-63D6-489C-8972-E600AD6BD9EA}" name="k"/>
+    <tableColumn id="10" xr3:uid="{48B991D0-E48E-4F51-8DA0-CB7229800EA6}" name="l"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -543,10 +572,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811DB032-1DCA-449C-9038-7B7A3A498C61}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="10.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +627,29 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>-6.4000000000000001E-2</v>
+        <v>-0.61</v>
       </c>
       <c r="B5" s="1">
-        <v>2.145</v>
+        <v>1.2776000000000001</v>
       </c>
       <c r="C5" s="1">
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="D5">
+        <v>-3.6999999999999998E-2</v>
+      </c>
+      <c r="D5" s="1">
         <f>SQRT(A5^2+B5^2+C5^2)</f>
-        <v>2.1459603910603753</v>
-      </c>
-      <c r="E5">
+        <v>1.4162382426696436</v>
+      </c>
+      <c r="E5" s="1">
         <f>2*PI()/D5</f>
-        <v>2.9279129910104724</v>
-      </c>
-      <c r="F5">
+        <v>4.4365313108164832</v>
+      </c>
+      <c r="F5" s="1">
         <f>DEGREES(2*ASIN($F$2/(2*E5)))</f>
-        <v>48.605228839417563</v>
-      </c>
+        <v>31.520019173072814</v>
+      </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
@@ -627,330 +659,450 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>-3.972</v>
-      </c>
-      <c r="B6" s="1">
-        <v>-1.7649999999999999</v>
-      </c>
-      <c r="C6" s="1">
-        <v>-0.15490000000000001</v>
-      </c>
-      <c r="D6">
+      <c r="A6" s="2">
+        <v>-1.714</v>
+      </c>
+      <c r="B6" s="2">
+        <v>-0.46179999999999999</v>
+      </c>
+      <c r="C6" s="2">
+        <v>-6.9000000000000006E-2</v>
+      </c>
+      <c r="D6" s="2">
         <f>SQRT(A6^2+B6^2+C6^2)</f>
-        <v>4.3492531554279523</v>
-      </c>
-      <c r="E6">
+        <v>1.776461719261071</v>
+      </c>
+      <c r="E6" s="2">
         <f>2*PI()/D6</f>
-        <v>1.4446584465514611</v>
-      </c>
-      <c r="F6">
+        <v>3.5369100493722496</v>
+      </c>
+      <c r="F6" s="2">
         <f>DEGREES(2*ASIN($F$2/(2*E6)))</f>
-        <v>113.0459740830986</v>
-      </c>
-      <c r="H6" s="1">
+        <v>39.838184906229607</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
         <v>4</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>-5.1999999999999998E-2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2.1373000000000002</v>
+      </c>
+      <c r="C7" s="1">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>SQRT(A7^2+B7^2+C7^2)</f>
+        <v>2.137985100509356</v>
+      </c>
+      <c r="E7" s="1">
+        <f>2*PI()/D7</f>
+        <v>2.938834936540331</v>
+      </c>
+      <c r="F7" s="1">
+        <f>DEGREES(2*ASIN($F$2/(2*E7)))</f>
+        <v>48.412990318321839</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>-1.752</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1.6875</v>
+      </c>
+      <c r="C8" s="1">
+        <v>-6.4000000000000001E-2</v>
+      </c>
+      <c r="D8" s="1">
+        <f>SQRT(A8^2+B8^2+C8^2)</f>
+        <v>2.4333631562099396</v>
+      </c>
+      <c r="E8" s="1">
+        <f>2*PI()/D8</f>
+        <v>2.5820993020071441</v>
+      </c>
+      <c r="F8" s="1">
+        <f>DEGREES(2*ASIN($F$2/(2*E8)))</f>
+        <v>55.637298479155213</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
         <v>-4</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>-4.0270000000000001</v>
-      </c>
-      <c r="B7">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="C7">
-        <v>-0.16489999999999999</v>
-      </c>
-      <c r="D7">
-        <f t="shared" ref="D7:D23" si="0">SQRT(A7^2+B7^2+C7^2)</f>
-        <v>4.048626558476343</v>
-      </c>
-      <c r="E7">
-        <f t="shared" ref="E7:E23" si="1">2*PI()/D7</f>
-        <v>1.5519300721932219</v>
-      </c>
-      <c r="F7">
-        <f t="shared" ref="F7:F23" si="2">DEGREES(2*ASIN($F$2/(2*E7)))</f>
-        <v>101.87381673624584</v>
-      </c>
-      <c r="H7">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>-2.3149999999999999</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.82779999999999998</v>
+      </c>
+      <c r="C9" s="1">
+        <v>-0.08</v>
+      </c>
+      <c r="D9" s="1">
+        <f>SQRT(A9^2+B9^2+C9^2)</f>
+        <v>2.4598532151329677</v>
+      </c>
+      <c r="E9" s="1">
+        <f>2*PI()/D9</f>
+        <v>2.5542927799616479</v>
+      </c>
+      <c r="F9" s="1">
+        <f>DEGREES(2*ASIN($F$2/(2*E9)))</f>
+        <v>56.296535760021541</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
+        <v>4</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>-1.21</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2.5571999999999999</v>
+      </c>
+      <c r="C10" s="1">
+        <v>-3.6999999999999998E-2</v>
+      </c>
+      <c r="D10" s="1">
+        <f>SQRT(A10^2+B10^2+C10^2)</f>
+        <v>2.8292650706499738</v>
+      </c>
+      <c r="E10" s="1">
+        <f>2*PI()/D10</f>
+        <v>2.2207835428216471</v>
+      </c>
+      <c r="F10" s="1">
+        <f>DEGREES(2*ASIN($F$2/(2*E10)))</f>
+        <v>65.721791294985735</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>-2.8610000000000002</v>
+      </c>
+      <c r="B11" s="1">
+        <v>-3.2000000000000001E-2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-0.107</v>
+      </c>
+      <c r="D11" s="1">
+        <f>SQRT(A11^2+B11^2+C11^2)</f>
+        <v>2.8631790024376755</v>
+      </c>
+      <c r="E11" s="1">
+        <f>2*PI()/D11</f>
+        <v>2.1944786902356292</v>
+      </c>
+      <c r="F11" s="1">
+        <f>DEGREES(2*ASIN($F$2/(2*E11)))</f>
+        <v>66.611316408933178</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
+        <v>6</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>-2.81</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-2.1812999999999998</v>
+      </c>
+      <c r="C12" s="1">
+        <v>-0.12</v>
+      </c>
+      <c r="D12" s="1">
+        <f>SQRT(A12^2+B12^2+C12^2)</f>
+        <v>3.5592934256675157</v>
+      </c>
+      <c r="E12" s="1">
+        <f>2*PI()/D12</f>
+        <v>1.7652900606252286</v>
+      </c>
+      <c r="F12" s="1">
+        <f>DEGREES(2*ASIN($F$2/(2*E12)))</f>
+        <v>86.095458819672444</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
         <v>8</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>-2.9260000000000002</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2.1173000000000002</v>
+      </c>
+      <c r="C13" s="1">
+        <v>-0.09</v>
+      </c>
+      <c r="D13" s="1">
+        <f>SQRT(A13^2+B13^2+C13^2)</f>
+        <v>3.6128292638872384</v>
+      </c>
+      <c r="E13" s="1">
+        <f>2*PI()/D13</f>
+        <v>1.7391315360469506</v>
+      </c>
+      <c r="F13" s="1">
+        <f>DEGREES(2*ASIN($F$2/(2*E13)))</f>
+        <v>87.716176526536088</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
+        <v>4</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
         <v>-6</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>-1.7050000000000001</v>
-      </c>
-      <c r="B8">
-        <v>-0.45300000000000001</v>
-      </c>
-      <c r="C8">
-        <v>-8.4900000000000003E-2</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>1.7661942163873146</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="1"/>
-        <v>3.5574713408537884</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="2"/>
-        <v>39.598273052151043</v>
-      </c>
-      <c r="H8">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>-3.4620000000000002</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1.2576000000000001</v>
+      </c>
+      <c r="C14" s="1">
+        <v>-0.123</v>
+      </c>
+      <c r="D14" s="1">
+        <f>SQRT(A14^2+B14^2+C14^2)</f>
+        <v>3.6853942475670092</v>
+      </c>
+      <c r="E14" s="1">
+        <f>2*PI()/D14</f>
+        <v>1.7048882385724577</v>
+      </c>
+      <c r="F14" s="1">
+        <f>DEGREES(2*ASIN($F$2/(2*E14)))</f>
+        <v>89.948868904452766</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>-2.379</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2.9870000000000001</v>
+      </c>
+      <c r="C15" s="1">
+        <v>-7.3999999999999996E-2</v>
+      </c>
+      <c r="D15" s="1">
+        <f>SQRT(A15^2+B15^2+C15^2)</f>
+        <v>3.8193305696155706</v>
+      </c>
+      <c r="E15" s="1">
+        <f>2*PI()/D15</f>
+        <v>1.6451012010233017</v>
+      </c>
+      <c r="F15" s="1">
+        <f>DEGREES(2*ASIN($F$2/(2*E15)))</f>
+        <v>94.189030827168281</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>-4.0369999999999999</v>
+      </c>
+      <c r="B16">
+        <v>0.37790000000000001</v>
+      </c>
+      <c r="C16">
+        <v>-0.13700000000000001</v>
+      </c>
+      <c r="D16">
+        <f>SQRT(A16^2+B16^2+C16^2)</f>
+        <v>4.0569627074943639</v>
+      </c>
+      <c r="E16">
+        <f>2*PI()/D16</f>
+        <v>1.5487412037514556</v>
+      </c>
+      <c r="F16">
+        <f>DEGREES(2*ASIN($F$2/(2*E16)))</f>
+        <v>102.16498524686074</v>
+      </c>
+      <c r="H16">
+        <v>8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>-1.8320000000000001</v>
+      </c>
+      <c r="B17">
+        <v>3.8567999999999998</v>
+      </c>
+      <c r="C17">
+        <v>-5.2999999999999999E-2</v>
+      </c>
+      <c r="D17">
+        <f>SQRT(A17^2+B17^2+C17^2)</f>
+        <v>4.270121689132524</v>
+      </c>
+      <c r="E17">
+        <f>2*PI()/D17</f>
+        <v>1.4714300351604304</v>
+      </c>
+      <c r="F17">
+        <f>DEGREES(2*ASIN($F$2/(2*E17)))</f>
+        <v>109.95589573386098</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>-3.9710000000000001</v>
+      </c>
+      <c r="B18" s="2">
+        <v>-1.7614000000000001</v>
+      </c>
+      <c r="C18" s="2">
+        <v>-0.14399999999999999</v>
+      </c>
+      <c r="D18" s="2">
+        <f>SQRT(A18^2+B18^2+C18^2)</f>
+        <v>4.346505143215639</v>
+      </c>
+      <c r="E18" s="2">
+        <f>2*PI()/D18</f>
+        <v>1.4455718100292294</v>
+      </c>
+      <c r="F18" s="2">
+        <f>DEGREES(2*ASIN($F$2/(2*E18)))</f>
+        <v>112.93656862004475</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2">
         <v>4</v>
       </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>-4.47</v>
-      </c>
-      <c r="B9">
-        <v>-0.27189999999999998</v>
-      </c>
-      <c r="C9">
-        <v>0.317</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>4.4894675196508551</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="1"/>
-        <v>1.399539094486695</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="2"/>
-        <v>118.85758906897046</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E10" t="e">
-        <f t="shared" si="1"/>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <f>SQRT(A19^2+B19^2+C19^2)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" t="e">
+        <f>2*PI()/D19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E11" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F11" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E12" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F12" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E13" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F13" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E14" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F14" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E15" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F15" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E16" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F16" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E17" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F17" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E18" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F18" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E19" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="F19" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E20" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F20" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="21" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E21" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F21" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E22" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F22" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E23" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F23" t="e">
-        <f t="shared" si="2"/>
+        <f>DEGREES(2*ASIN($F$2/(2*E19)))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>